--- a/results/08-2025/beta/inputs-08-2025.xlsx
+++ b/results/08-2025/beta/inputs-08-2025.xlsx
@@ -33418,7 +33418,7 @@
         <v>81.5</v>
       </c>
       <c r="V204" t="n">
-        <v>1862.5</v>
+        <v>1804.1</v>
       </c>
       <c r="W204" t="n">
         <v>159.5</v>
@@ -33472,7 +33472,7 @@
         <v>-26.68</v>
       </c>
       <c r="AN204" t="n">
-        <v>1485.7875</v>
+        <v>1472.6475</v>
       </c>
       <c r="AO204" t="n">
         <v>139.95</v>
@@ -33576,7 +33576,7 @@
         <v>82.4</v>
       </c>
       <c r="V205" t="n">
-        <v>1721.9</v>
+        <v>1687.4</v>
       </c>
       <c r="W205" t="n">
         <v>161.7</v>
@@ -33630,7 +33630,7 @@
         <v>-27.61</v>
       </c>
       <c r="AN205" t="n">
-        <v>1531.035</v>
+        <v>1510.1325</v>
       </c>
       <c r="AO205" t="n">
         <v>142.245</v>
@@ -33734,7 +33734,7 @@
         <v>83.1</v>
       </c>
       <c r="V206" t="n">
-        <v>1968.7</v>
+        <v>1947.3</v>
       </c>
       <c r="W206" t="n">
         <v>164.8</v>
@@ -33788,7 +33788,7 @@
         <v>-28.55</v>
       </c>
       <c r="AN206" t="n">
-        <v>1620.54</v>
+        <v>1594.8225</v>
       </c>
       <c r="AO206" t="n">
         <v>144.6075</v>
@@ -33892,7 +33892,7 @@
         <v>93.7</v>
       </c>
       <c r="V207" t="n">
-        <v>1761.77816</v>
+        <v>1748.47816</v>
       </c>
       <c r="W207" t="n">
         <v>168.2</v>
@@ -33946,7 +33946,7 @@
         <v>-29.66</v>
       </c>
       <c r="AN207" t="n">
-        <v>1645.847586</v>
+        <v>1617.137586</v>
       </c>
       <c r="AO207" t="n">
         <v>147.195</v>
@@ -34050,7 +34050,7 @@
         <v>119.3</v>
       </c>
       <c r="V208" t="n">
-        <v>1938.02984</v>
+        <v>1919.32984</v>
       </c>
       <c r="W208" t="n">
         <v>174.6</v>
@@ -34104,7 +34104,7 @@
         <v>-31.5833333333333</v>
       </c>
       <c r="AN208" t="n">
-        <v>1662.8418</v>
+        <v>1643.0643</v>
       </c>
       <c r="AO208" t="n">
         <v>150.5925</v>
@@ -34208,7 +34208,7 @@
         <v>168.1</v>
       </c>
       <c r="V209" t="n">
-        <v>1931.724</v>
+        <v>1899.524</v>
       </c>
       <c r="W209" t="n">
         <v>177.2</v>
@@ -34262,7 +34262,7 @@
         <v>-35.0666666666666</v>
       </c>
       <c r="AN209" t="n">
-        <v>1710.0522</v>
+        <v>1690.7922</v>
       </c>
       <c r="AO209" t="n">
         <v>154.08</v>
@@ -34366,7 +34366,7 @@
         <v>170.8</v>
       </c>
       <c r="V210" t="n">
-        <v>1956.324</v>
+        <v>1929.424</v>
       </c>
       <c r="W210" t="n">
         <v>181.7</v>
@@ -34420,7 +34420,7 @@
         <v>-38.3666666666666</v>
       </c>
       <c r="AN210" t="n">
-        <v>1707.2676</v>
+        <v>1686.7701</v>
       </c>
       <c r="AO210" t="n">
         <v>157.8825</v>
@@ -34524,7 +34524,7 @@
         <v>157.6</v>
       </c>
       <c r="V211" t="n">
-        <v>1955.424</v>
+        <v>1935.424</v>
       </c>
       <c r="W211" t="n">
         <v>191.3</v>
@@ -34578,7 +34578,7 @@
         <v>-41.06</v>
       </c>
       <c r="AN211" t="n">
-        <v>1750.837914</v>
+        <v>1728.832914</v>
       </c>
       <c r="AO211" t="n">
         <v>163.08</v>
@@ -34682,7 +34682,7 @@
         <v>159.1</v>
       </c>
       <c r="V212" t="n">
-        <v>1937.424</v>
+        <v>1929.324</v>
       </c>
       <c r="W212" t="n">
         <v>213.6</v>
@@ -34736,7 +34736,7 @@
         <v>-43.8933333333333</v>
       </c>
       <c r="AN212" t="n">
-        <v>1750.7016</v>
+        <v>1731.0816</v>
       </c>
       <c r="AO212" t="n">
         <v>171.855</v>
@@ -34840,7 +34840,7 @@
         <v>162.2</v>
       </c>
       <c r="V213" t="n">
-        <v>2008.584</v>
+        <v>2003.684</v>
       </c>
       <c r="W213" t="n">
         <v>269.1</v>
@@ -34894,7 +34894,7 @@
         <v>-46.9566666666666</v>
       </c>
       <c r="AN213" t="n">
-        <v>1767.9951</v>
+        <v>1754.5176</v>
       </c>
       <c r="AO213" t="n">
         <v>192.5325</v>
@@ -35052,7 +35052,7 @@
         <v>-50.0966666666666</v>
       </c>
       <c r="AN214" t="n">
-        <v>1780.9236</v>
+        <v>1773.4986</v>
       </c>
       <c r="AO214" t="n">
         <v>197.91</v>
@@ -35210,7 +35210,7 @@
         <v>-53.2966666666666</v>
       </c>
       <c r="AN215" t="n">
-        <v>1791.6111</v>
+        <v>1788.6861</v>
       </c>
       <c r="AO215" t="n">
         <v>199.755</v>
@@ -35368,7 +35368,7 @@
         <v>-56.1099999999999</v>
       </c>
       <c r="AN216" t="n">
-        <v>1808.7786</v>
+        <v>1807.6761</v>
       </c>
       <c r="AO216" t="n">
         <v>197.19</v>
@@ -36366,34 +36366,34 @@
         <v>-1</v>
       </c>
       <c r="D223" t="n">
-        <v>0.0149204426581513</v>
+        <v>0.0173193541029251</v>
       </c>
       <c r="E223" t="n">
-        <v>0.00175881733093664</v>
+        <v>0.00230893200272742</v>
       </c>
       <c r="F223" t="n">
-        <v>0.00126785439461785</v>
+        <v>0.00370829088830416</v>
       </c>
       <c r="G223" t="n">
-        <v>0.00165780203080734</v>
+        <v>0.00258647816843571</v>
       </c>
       <c r="H223" t="n">
-        <v>0.00515919459239966</v>
+        <v>0.00498403675129988</v>
       </c>
       <c r="I223" t="n">
         <v>0.00571780133544419</v>
       </c>
       <c r="J223" t="n">
-        <v>30331.1</v>
+        <v>30353.9</v>
       </c>
       <c r="K223" t="n">
-        <v>20640.9</v>
+        <v>20643.9</v>
       </c>
       <c r="L223" t="n">
         <v>-0.3</v>
       </c>
       <c r="M223" t="n">
-        <v>1938.7</v>
+        <v>1938.3</v>
       </c>
       <c r="N223" t="n">
         <v>400.7276195</v>
@@ -36402,13 +36402,13 @@
         <v>75.203</v>
       </c>
       <c r="P223" t="n">
-        <v>3251</v>
+        <v>3250.7</v>
       </c>
       <c r="Q223" t="n">
-        <v>4871.2</v>
+        <v>4871.4</v>
       </c>
       <c r="R223" t="n">
-        <v>2584.7</v>
+        <v>2589.6</v>
       </c>
       <c r="S223" t="n">
         <v>0</v>
@@ -36420,10 +36420,10 @@
         <v>0</v>
       </c>
       <c r="V223" t="n">
-        <v>2352.098</v>
+        <v>2354.298</v>
       </c>
       <c r="W223" t="n">
-        <v>218.9</v>
+        <v>219.1</v>
       </c>
       <c r="X223" t="n">
         <v>0</v>
@@ -36459,13 +36459,13 @@
         <v>1862.758</v>
       </c>
       <c r="AI223" t="n">
-        <v>302.442</v>
+        <v>303.742</v>
       </c>
       <c r="AJ223" t="n">
-        <v>-2721.972</v>
+        <v>-2721.996</v>
       </c>
       <c r="AK223" t="n">
-        <v>-1489.914</v>
+        <v>-1490.502</v>
       </c>
       <c r="AL223" t="n">
         <v>-168.926666666667</v>
@@ -36474,10 +36474,10 @@
         <v>-60.3699999999999</v>
       </c>
       <c r="AN223" t="n">
-        <v>2010.733425</v>
+        <v>2011.228425</v>
       </c>
       <c r="AO223" t="n">
-        <v>197.28</v>
+        <v>197.325</v>
       </c>
       <c r="AP223" t="n">
         <v>0</v>
@@ -36510,7 +36510,7 @@
         <v>1612.17</v>
       </c>
       <c r="AZ223" t="n">
-        <v>268.605</v>
+        <v>268.8975</v>
       </c>
     </row>
     <row r="224">
@@ -36536,22 +36536,22 @@
         <v>0.00774551207611962</v>
       </c>
       <c r="H224" t="n">
-        <v>0.00591602658436119</v>
+        <v>0.0061860942661327</v>
       </c>
       <c r="I224" t="n">
         <v>0.00573662843673683</v>
       </c>
       <c r="J224" t="n">
-        <v>30633.6710925302</v>
+        <v>30656.698536339</v>
       </c>
       <c r="K224" t="n">
-        <v>20845.4871147455</v>
+        <v>20848.5168499482</v>
       </c>
       <c r="L224" t="n">
         <v>-0.3</v>
       </c>
       <c r="M224" t="n">
-        <v>1963.86342701628</v>
+        <v>1963.45823520176</v>
       </c>
       <c r="N224" t="n">
         <v>403.2265501007</v>
@@ -36560,25 +36560,25 @@
         <v>75.203</v>
       </c>
       <c r="P224" t="n">
-        <v>3280.71074023201</v>
+        <v>3280.40799854573</v>
       </c>
       <c r="Q224" t="n">
-        <v>4884.27813591109</v>
+        <v>4884.47935141435</v>
       </c>
       <c r="R224" t="n">
-        <v>2610.41793496548</v>
+        <v>2615.31340452966</v>
       </c>
       <c r="S224" t="n">
-        <v>140.192005864581</v>
+        <v>142.436865609892</v>
       </c>
       <c r="T224" t="n">
         <v>103.083510693309</v>
       </c>
       <c r="U224" t="n">
-        <v>172.442000465766</v>
+        <v>159.084364030707</v>
       </c>
       <c r="V224" t="n">
-        <v>2359.387155</v>
+        <v>2341.58714</v>
       </c>
       <c r="W224" t="n">
         <v>234.744608694576</v>
@@ -36614,28 +36614,28 @@
         <v>0</v>
       </c>
       <c r="AH224" t="n">
-        <v>1884.43061146495</v>
+        <v>1899.08959440996</v>
       </c>
       <c r="AI224" t="n">
-        <v>312.682511280734</v>
+        <v>313.324861669376</v>
       </c>
       <c r="AJ224" t="n">
-        <v>-2774.60137630933</v>
+        <v>-2774.64952216972</v>
       </c>
       <c r="AK224" t="n">
-        <v>-1509.09215219586</v>
+        <v>-1510.26760854356</v>
       </c>
       <c r="AL224" t="n">
-        <v>-160.193066862153</v>
+        <v>-160.26789552033</v>
       </c>
       <c r="AM224" t="n">
-        <v>-60.8147333488588</v>
+        <v>-60.3694788010235</v>
       </c>
       <c r="AN224" t="n">
-        <v>2057.350759875</v>
+        <v>2053.8407565</v>
       </c>
       <c r="AO224" t="n">
-        <v>200.23753695628</v>
+        <v>200.28253695628</v>
       </c>
       <c r="AP224" t="n">
         <v>0</v>
@@ -36665,10 +36665,10 @@
         <v>0.28035</v>
       </c>
       <c r="AY224" t="n">
-        <v>1646.59356257961</v>
+        <v>1649.89183374224</v>
       </c>
       <c r="AZ224" t="n">
-        <v>273.446890038165</v>
+        <v>273.88391887561</v>
       </c>
     </row>
     <row r="225">
@@ -36694,22 +36694,22 @@
         <v>0.00800202664149885</v>
       </c>
       <c r="H225" t="n">
-        <v>0.0059495417545925</v>
+        <v>0.00644036325116937</v>
       </c>
       <c r="I225" t="n">
         <v>0.00571666765914358</v>
       </c>
       <c r="J225" t="n">
-        <v>30927.2311333305</v>
+        <v>30950.4792473072</v>
       </c>
       <c r="K225" t="n">
-        <v>21042.9746766333</v>
+        <v>21046.0331151718</v>
       </c>
       <c r="L225" t="n">
         <v>-0.3</v>
       </c>
       <c r="M225" t="n">
-        <v>1975.63341707228</v>
+        <v>1949.86467263307</v>
       </c>
       <c r="N225" t="n">
         <v>401.864404763182</v>
@@ -36718,25 +36718,25 @@
         <v>75.203</v>
       </c>
       <c r="P225" t="n">
-        <v>3311.53068818719</v>
+        <v>3311.22510245773</v>
       </c>
       <c r="Q225" t="n">
-        <v>4968.92969341018</v>
+        <v>4969.1321320524</v>
       </c>
       <c r="R225" t="n">
-        <v>2637.25905250979</v>
+        <v>2642.20175235986</v>
       </c>
       <c r="S225" t="n">
-        <v>394.325777053842</v>
+        <v>396.556766092507</v>
       </c>
       <c r="T225" t="n">
         <v>109.658761987664</v>
       </c>
       <c r="U225" t="n">
-        <v>172.355545528645</v>
+        <v>159.004606032933</v>
       </c>
       <c r="V225" t="n">
-        <v>2351.492755775</v>
+        <v>2333.6927257</v>
       </c>
       <c r="W225" t="n">
         <v>238.176195410118</v>
@@ -36772,28 +36772,28 @@
         <v>0</v>
       </c>
       <c r="AH225" t="n">
-        <v>1912.00537081367</v>
+        <v>1934.074188875</v>
       </c>
       <c r="AI225" t="n">
-        <v>317.233052316878</v>
+        <v>317.975782256626</v>
       </c>
       <c r="AJ225" t="n">
-        <v>-2821.33893951855</v>
+        <v>-2821.39937801601</v>
       </c>
       <c r="AK225" t="n">
-        <v>-1527.72923849703</v>
+        <v>-1529.20381882674</v>
       </c>
       <c r="AL225" t="n">
-        <v>-159.773926097281</v>
+        <v>-159.923121056746</v>
       </c>
       <c r="AM225" t="n">
-        <v>-61.153251533147</v>
+        <v>-60.2629656687879</v>
       </c>
       <c r="AN225" t="n">
-        <v>2098.18707992438</v>
+        <v>2090.6720697825</v>
       </c>
       <c r="AO225" t="n">
-        <v>204.844680923556</v>
+        <v>204.889680923556</v>
       </c>
       <c r="AP225" t="n">
         <v>0</v>
@@ -36823,10 +36823,10 @@
         <v>0.250425</v>
       </c>
       <c r="AY225" t="n">
-        <v>1677.71789601269</v>
+        <v>1685.98165123911</v>
       </c>
       <c r="AZ225" t="n">
-        <v>279.658701809463</v>
+        <v>280.26284488335</v>
       </c>
     </row>
     <row r="226">
@@ -36852,22 +36852,22 @@
         <v>0.00818999490559191</v>
       </c>
       <c r="H226" t="n">
-        <v>0.0053246047022768</v>
+        <v>0.00557056312403703</v>
       </c>
       <c r="I226" t="n">
         <v>0.00567994383495618</v>
       </c>
       <c r="J226" t="n">
-        <v>31230.5030854396</v>
+        <v>31253.9791700639</v>
       </c>
       <c r="K226" t="n">
-        <v>21223.0633343345</v>
+        <v>21226.1479474087</v>
       </c>
       <c r="L226" t="n">
         <v>-0.3</v>
       </c>
       <c r="M226" t="n">
-        <v>2011.14631810331</v>
+        <v>1975.22579682839</v>
       </c>
       <c r="N226" t="n">
         <v>404.538965016832</v>
@@ -36876,25 +36876,25 @@
         <v>75.203</v>
       </c>
       <c r="P226" t="n">
-        <v>3343.22764975842</v>
+        <v>3342.91913905558</v>
       </c>
       <c r="Q226" t="n">
-        <v>4977.93145125724</v>
+        <v>4978.03405211661</v>
       </c>
       <c r="R226" t="n">
-        <v>2661.94500876973</v>
+        <v>2666.93086481898</v>
       </c>
       <c r="S226" t="n">
-        <v>391.889287563627</v>
+        <v>394.106491601002</v>
       </c>
       <c r="T226" t="n">
         <v>134.709036355557</v>
       </c>
       <c r="U226" t="n">
-        <v>172.564054494644</v>
+        <v>159.196963556976</v>
       </c>
       <c r="V226" t="n">
-        <v>2405.12553055388</v>
+        <v>2386.8834023285</v>
       </c>
       <c r="W226" t="n">
         <v>241.657946376297</v>
@@ -36930,28 +36930,28 @@
         <v>0</v>
       </c>
       <c r="AH226" t="n">
-        <v>1938.51561009222</v>
+        <v>1968.23820716732</v>
       </c>
       <c r="AI226" t="n">
-        <v>323.36378624361</v>
+        <v>324.226687835</v>
       </c>
       <c r="AJ226" t="n">
-        <v>-2861.79002551476</v>
+        <v>-2861.85070318514</v>
       </c>
       <c r="AK226" t="n">
-        <v>-1546.81956345147</v>
+        <v>-1548.59871833324</v>
       </c>
       <c r="AL226" t="n">
-        <v>-158.360235682735</v>
+        <v>-158.583337443447</v>
       </c>
       <c r="AM226" t="n">
-        <v>-61.6153866829684</v>
+        <v>-60.2795311206871</v>
       </c>
       <c r="AN226" t="n">
-        <v>2130.323274299</v>
+        <v>2118.70378530641</v>
       </c>
       <c r="AO226" t="n">
-        <v>210.032718858223</v>
+        <v>210.077718858223</v>
       </c>
       <c r="AP226" t="n">
         <v>0</v>
@@ -36981,10 +36981,10 @@
         <v>0.222075</v>
       </c>
       <c r="AY226" t="n">
-        <v>1709.48465828344</v>
+        <v>1724.43599785176</v>
       </c>
       <c r="AZ226" t="n">
-        <v>282.537303714275</v>
+        <v>283.335599646225</v>
       </c>
     </row>
     <row r="227">
@@ -37010,22 +37010,22 @@
         <v>0.00776550468724246</v>
       </c>
       <c r="H227" t="n">
-        <v>0.00505601510080766</v>
+        <v>0.0053021706673404</v>
       </c>
       <c r="I227" t="n">
         <v>0.0056310426470525</v>
       </c>
       <c r="J227" t="n">
-        <v>31532.8739323758</v>
+        <v>31556.5773102836</v>
       </c>
       <c r="K227" t="n">
-        <v>21417.6510788579</v>
+        <v>21420.7639738012</v>
       </c>
       <c r="L227" t="n">
         <v>-0.2</v>
       </c>
       <c r="M227" t="n">
-        <v>2026.77199455697</v>
+        <v>1995.92047417177</v>
       </c>
       <c r="N227" t="n">
         <v>404.4368788</v>
@@ -37034,25 +37034,25 @@
         <v>75.203</v>
       </c>
       <c r="P227" t="n">
-        <v>3372.78044478709</v>
+        <v>3372.46920697305</v>
       </c>
       <c r="Q227" t="n">
-        <v>5018.68661604681</v>
+        <v>5018.7903873748</v>
       </c>
       <c r="R227" t="n">
-        <v>2687.62095094217</v>
+        <v>2692.65301515888</v>
       </c>
       <c r="S227" t="n">
-        <v>389.467852836203</v>
+        <v>391.671357048081</v>
       </c>
       <c r="T227" t="n">
         <v>155.206844624839</v>
       </c>
       <c r="U227" t="n">
-        <v>172.904788658593</v>
+        <v>159.511303901144</v>
       </c>
       <c r="V227" t="n">
-        <v>2420.73626997664</v>
+        <v>2402.49412652514</v>
       </c>
       <c r="W227" t="n">
         <v>245.190594913367</v>
@@ -37088,25 +37088,25 @@
         <v>0</v>
       </c>
       <c r="AH227" t="n">
-        <v>1969.6219827834</v>
+        <v>2007.2538143685</v>
       </c>
       <c r="AI227" t="n">
-        <v>325.376600965333</v>
+        <v>326.375057593894</v>
       </c>
       <c r="AJ227" t="n">
-        <v>-2900.86463783576</v>
+        <v>-2900.92562174698</v>
       </c>
       <c r="AK227" t="n">
-        <v>-1564.75853441394</v>
+        <v>-1566.84497501071</v>
       </c>
       <c r="AL227" t="n">
-        <v>-157.029164110608</v>
+        <v>-157.325716011716</v>
       </c>
       <c r="AM227" t="n">
-        <v>-61.9655463049215</v>
+        <v>-60.1832412507253</v>
       </c>
       <c r="AN227" t="n">
-        <v>2145.76688504374</v>
+        <v>2129.54791377457</v>
       </c>
       <c r="AO227" t="n">
         <v>215.94810271373</v>
@@ -37139,10 +37139,10 @@
         <v>0.1953</v>
       </c>
       <c r="AY227" t="n">
-        <v>1733.52905440971</v>
+        <v>1756.94755608467</v>
       </c>
       <c r="AZ227" t="n">
-        <v>287.697588931475</v>
+        <v>288.428037604852</v>
       </c>
     </row>
     <row r="228">
@@ -37168,22 +37168,22 @@
         <v>0.0076646909789202</v>
       </c>
       <c r="H228" t="n">
-        <v>0.00504006731362838</v>
+        <v>0.00528623459246003</v>
       </c>
       <c r="I228" t="n">
         <v>0.00558696597638098</v>
       </c>
       <c r="J228" t="n">
-        <v>31828.6366747101</v>
+        <v>31852.5623785647</v>
       </c>
       <c r="K228" t="n">
-        <v>21587.7403663369</v>
+        <v>21590.8779824825</v>
       </c>
       <c r="L228" t="n">
         <v>-0.2</v>
       </c>
       <c r="M228" t="n">
-        <v>2044.22404877794</v>
+        <v>2013.36892761815</v>
       </c>
       <c r="N228" t="n">
         <v>408.164405784728</v>
@@ -37192,25 +37192,25 @@
         <v>75.203</v>
       </c>
       <c r="P228" t="n">
-        <v>3402.89007687522</v>
+        <v>3402.57606056545</v>
       </c>
       <c r="Q228" t="n">
-        <v>5059.83103467339</v>
+        <v>5059.93598982268</v>
       </c>
       <c r="R228" t="n">
-        <v>2711.06551750846</v>
+        <v>2716.13839676083</v>
       </c>
       <c r="S228" t="n">
-        <v>387.061379850081</v>
+        <v>389.251268885963</v>
       </c>
       <c r="T228" t="n">
         <v>162.820344255939</v>
       </c>
       <c r="U228" t="n">
-        <v>172.73187878435</v>
+        <v>159.351787905596</v>
       </c>
       <c r="V228" t="n">
-        <v>2438.09170309653</v>
+        <v>2419.84954434277</v>
       </c>
       <c r="W228" t="n">
         <v>248.77488506154</v>
@@ -37246,25 +37246,25 @@
         <v>0</v>
       </c>
       <c r="AH228" t="n">
-        <v>1997.46782381642</v>
+        <v>2043.49594294431</v>
       </c>
       <c r="AI228" t="n">
-        <v>331.135171796343</v>
+        <v>332.060239499914</v>
       </c>
       <c r="AJ228" t="n">
-        <v>-2941.97847492114</v>
+        <v>-2942.0458973987</v>
       </c>
       <c r="AK228" t="n">
-        <v>-1581.71969598878</v>
+        <v>-1584.11573073287</v>
       </c>
       <c r="AL228" t="n">
-        <v>-154.867876772278</v>
+        <v>-155.237424974581</v>
       </c>
       <c r="AM228" t="n">
-        <v>-62.1932755977332</v>
+        <v>-59.9649675142452</v>
       </c>
       <c r="AN228" t="n">
-        <v>2163.47540836546</v>
+        <v>2147.15695475169</v>
       </c>
       <c r="AO228" t="n">
         <v>219.104914896297</v>
@@ -37297,10 +37297,10 @@
         <v>0.171675</v>
       </c>
       <c r="AY228" t="n">
-        <v>1758.96242718879</v>
+        <v>1789.4389845049</v>
       </c>
       <c r="AZ228" t="n">
-        <v>291.849437547487</v>
+        <v>292.643497616722</v>
       </c>
     </row>
     <row r="229">
@@ -37326,22 +37326,22 @@
         <v>0.00766526403461443</v>
       </c>
       <c r="H229" t="n">
-        <v>0.00506419440096284</v>
+        <v>0.00531034396078045</v>
       </c>
       <c r="I229" t="n">
         <v>0.00554760795794795</v>
       </c>
       <c r="J229" t="n">
-        <v>32125.9012589993</v>
+        <v>32150.0504177409</v>
       </c>
       <c r="K229" t="n">
-        <v>21780.4282305181</v>
+        <v>21783.5938523995</v>
       </c>
       <c r="L229" t="n">
         <v>-0.2</v>
       </c>
       <c r="M229" t="n">
-        <v>2054.57352279269</v>
+        <v>2023.71626628984</v>
       </c>
       <c r="N229" t="n">
         <v>409.918808201709</v>
@@ -37350,25 +37350,25 @@
         <v>75.203</v>
       </c>
       <c r="P229" t="n">
-        <v>3432.27406558326</v>
+        <v>3431.95733773962</v>
       </c>
       <c r="Q229" t="n">
-        <v>5101.36887514672</v>
+        <v>5101.47502762232</v>
       </c>
       <c r="R229" t="n">
-        <v>2736.45208782637</v>
+        <v>2741.5707090953</v>
       </c>
       <c r="S229" t="n">
-        <v>384.669776158537</v>
+        <v>386.846134144888</v>
       </c>
       <c r="T229" t="n">
         <v>160.445027356869</v>
       </c>
       <c r="U229" t="n">
-        <v>172.940387750349</v>
+        <v>159.54414542964</v>
       </c>
       <c r="V229" t="n">
-        <v>2447.30891338201</v>
+        <v>2429.06673924948</v>
       </c>
       <c r="W229" t="n">
         <v>252.41157173769</v>
@@ -37404,25 +37404,25 @@
         <v>0</v>
       </c>
       <c r="AH229" t="n">
-        <v>2014.7548505226</v>
+        <v>2061.45657192403</v>
       </c>
       <c r="AI229" t="n">
-        <v>330.366464938642</v>
+        <v>331.32591017766</v>
       </c>
       <c r="AJ229" t="n">
-        <v>-2981.04754297593</v>
+        <v>-2981.12147747089</v>
       </c>
       <c r="AK229" t="n">
-        <v>-1597.64868947141</v>
+        <v>-1600.35703491478</v>
       </c>
       <c r="AL229" t="n">
-        <v>-152.196869310896</v>
+        <v>-152.638962779411</v>
       </c>
       <c r="AM229" t="n">
-        <v>-62.3946218560782</v>
+        <v>-59.7197723618998</v>
       </c>
       <c r="AN229" t="n">
-        <v>2185.03404382704</v>
+        <v>2168.61610780033</v>
       </c>
       <c r="AO229" t="n">
         <v>222.307874570001</v>
@@ -37455,10 +37455,10 @@
         <v>0.14805</v>
       </c>
       <c r="AY229" t="n">
-        <v>1782.0810601233</v>
+        <v>1818.10002069094</v>
       </c>
       <c r="AZ229" t="n">
-        <v>294.804455387384</v>
+        <v>295.647276398955</v>
       </c>
     </row>
     <row r="230">
@@ -37490,16 +37490,16 @@
         <v>0.00550459474437348</v>
       </c>
       <c r="J230" t="n">
-        <v>32430.7751758605</v>
+        <v>32455.1535094524</v>
       </c>
       <c r="K230" t="n">
-        <v>21985.4153200725</v>
+        <v>21988.6107352898</v>
       </c>
       <c r="L230" t="n">
         <v>-0.1</v>
       </c>
       <c r="M230" t="n">
-        <v>2064.31420421835</v>
+        <v>2033.45493798084</v>
       </c>
       <c r="N230" t="n">
         <v>412.700350865505</v>
@@ -37508,25 +37508,25 @@
         <v>75.203</v>
       </c>
       <c r="P230" t="n">
-        <v>3461.01668426442</v>
+        <v>3460.69730407208</v>
       </c>
       <c r="Q230" t="n">
-        <v>5247.53110881393</v>
+        <v>5247.63847227491</v>
       </c>
       <c r="R230" t="n">
-        <v>2763.27850728241</v>
+        <v>2768.44571603214</v>
       </c>
       <c r="S230" t="n">
-        <v>392.292949886067</v>
+        <v>394.455860429545</v>
       </c>
       <c r="T230" t="n">
         <v>146.435353395161</v>
       </c>
       <c r="U230" t="n">
-        <v>172.609824755473</v>
+        <v>159.239188379327</v>
       </c>
       <c r="V230" t="n">
-        <v>2504.06277557692</v>
+        <v>2485.36833507973</v>
       </c>
       <c r="W230" t="n">
         <v>256.101420894358</v>
@@ -37562,25 +37562,25 @@
         <v>0</v>
       </c>
       <c r="AH230" t="n">
-        <v>2044.9908675864</v>
+        <v>2092.37846793142</v>
       </c>
       <c r="AI230" t="n">
-        <v>335.348548293239</v>
+        <v>336.34077716034</v>
       </c>
       <c r="AJ230" t="n">
-        <v>-3028.7194139532</v>
+        <v>-3028.79993475452</v>
       </c>
       <c r="AK230" t="n">
-        <v>-1613.54817929479</v>
+        <v>-1616.57221703298</v>
       </c>
       <c r="AL230" t="n">
-        <v>-149.943300973764</v>
+        <v>-150.457491460396</v>
       </c>
       <c r="AM230" t="n">
-        <v>-62.4682826812606</v>
+        <v>-59.3477453078774</v>
       </c>
       <c r="AN230" t="n">
-        <v>2207.29492395722</v>
+        <v>2190.77521766935</v>
       </c>
       <c r="AO230" t="n">
         <v>225.557656336565</v>
@@ -37613,10 +37613,10 @@
         <v>0.124425</v>
       </c>
       <c r="AY230" t="n">
-        <v>1806.03799305949</v>
+        <v>1846.03157936286</v>
       </c>
       <c r="AZ230" t="n">
-        <v>297.50102684855</v>
+        <v>298.372946497157</v>
       </c>
     </row>
     <row r="231">
@@ -37648,16 +37648,16 @@
         <v>0.00545389484594594</v>
       </c>
       <c r="J231" t="n">
-        <v>32727.5391461647</v>
+        <v>32752.1405583302</v>
       </c>
       <c r="K231" t="n">
-        <v>22168.3038014359</v>
+        <v>22171.5257981223</v>
       </c>
       <c r="L231" t="n">
         <v>-0.1</v>
       </c>
       <c r="M231" t="n">
-        <v>2075.57686711676</v>
+        <v>2044.71527712357</v>
       </c>
       <c r="N231" t="n">
         <v>415.5093012</v>
@@ -37666,25 +37666,25 @@
         <v>75.203</v>
       </c>
       <c r="P231" t="n">
-        <v>3490.55682467248</v>
+        <v>3490.23471853671</v>
       </c>
       <c r="Q231" t="n">
-        <v>5279.96277282185</v>
+        <v>5280.07090845169</v>
       </c>
       <c r="R231" t="n">
-        <v>2788.05586111262</v>
+        <v>2793.26677442623</v>
       </c>
       <c r="S231" t="n">
-        <v>389.869020979811</v>
+        <v>392.018567170476</v>
       </c>
       <c r="T231" t="n">
         <v>123.274912601363</v>
       </c>
       <c r="U231" t="n">
-        <v>171.974126688402</v>
+        <v>158.652732513342</v>
       </c>
       <c r="V231" t="n">
-        <v>2521.46879227051</v>
+        <v>2502.77433624038</v>
       </c>
       <c r="W231" t="n">
         <v>259.845209681073</v>
@@ -37720,25 +37720,25 @@
         <v>0</v>
       </c>
       <c r="AH231" t="n">
-        <v>2076.09258663117</v>
+        <v>2124.19162097592</v>
       </c>
       <c r="AI231" t="n">
-        <v>339.993837870728</v>
+        <v>341.004131904693</v>
       </c>
       <c r="AJ231" t="n">
-        <v>-3063.96081418302</v>
+        <v>-3064.03594211138</v>
       </c>
       <c r="AK231" t="n">
-        <v>-1628.84575735872</v>
+        <v>-1631.89398741841</v>
       </c>
       <c r="AL231" t="n">
-        <v>-146.492268339758</v>
+        <v>-147.078110366078</v>
       </c>
       <c r="AM231" t="n">
-        <v>-62.7340869042074</v>
+        <v>-59.1695030583221</v>
       </c>
       <c r="AN231" t="n">
-        <v>2229.95974147334</v>
+        <v>2213.33826485528</v>
       </c>
       <c r="AO231" t="n">
         <v>228.854944659299</v>
@@ -37771,10 +37771,10 @@
         <v>0.1008</v>
       </c>
       <c r="AY231" t="n">
-        <v>1829.99387892524</v>
+        <v>1872.34258584953</v>
       </c>
       <c r="AZ231" t="n">
-        <v>300.789905152264</v>
+        <v>301.664488217087</v>
       </c>
     </row>
     <row r="232">
@@ -37806,10 +37806,10 @@
         <v>0.00542022049047874</v>
       </c>
       <c r="J232" t="n">
-        <v>33027.907537161</v>
+        <v>33052.7347373564</v>
       </c>
       <c r="K232" t="n">
-        <v>22351.6922513104</v>
+        <v>22354.9409021325</v>
       </c>
       <c r="L232" t="n">
         <v>0</v>
@@ -37884,19 +37884,19 @@
         <v>0</v>
       </c>
       <c r="AJ232" t="n">
-        <v>-2456.05225949952</v>
+        <v>-2456.10887269003</v>
       </c>
       <c r="AK232" t="n">
-        <v>-1306.42397082385</v>
+        <v>-1308.86844018471</v>
       </c>
       <c r="AL232" t="n">
-        <v>-130.055601673092</v>
+        <v>-130.641443699412</v>
       </c>
       <c r="AM232" t="n">
-        <v>-57.3140869042074</v>
+        <v>-53.7495030583221</v>
       </c>
       <c r="AN232" t="n">
-        <v>1681.38910827663</v>
+        <v>1668.87211737816</v>
       </c>
       <c r="AO232" t="n">
         <v>172.880595520452</v>
@@ -37929,10 +37929,10 @@
         <v>0.0819</v>
       </c>
       <c r="AY232" t="n">
-        <v>1380.56361856654</v>
+        <v>1412.55599868706</v>
       </c>
       <c r="AZ232" t="n">
-        <v>226.284491498087</v>
+        <v>226.950934329606</v>
       </c>
     </row>
     <row r="233">
@@ -37964,10 +37964,10 @@
         <v>0.00537879404345354</v>
       </c>
       <c r="J233" t="n">
-        <v>33338.989067436</v>
+        <v>33364.0501087678</v>
       </c>
       <c r="K233" t="n">
-        <v>22548.2798698782</v>
+        <v>22551.5570932362</v>
       </c>
       <c r="L233" t="n">
         <v>0</v>
@@ -38042,19 +38042,19 @@
         <v>0</v>
       </c>
       <c r="AJ233" t="n">
-        <v>-1841.1187115256</v>
+        <v>-1841.15669025978</v>
       </c>
       <c r="AK233" t="n">
-        <v>-980.905076006506</v>
+        <v>-982.740328577541</v>
       </c>
       <c r="AL233" t="n">
-        <v>-112.985601673092</v>
+        <v>-113.571443699412</v>
       </c>
       <c r="AM233" t="n">
-        <v>-51.840753570874</v>
+        <v>-48.2761697249888</v>
       </c>
       <c r="AN233" t="n">
-        <v>1130.74460276567</v>
+        <v>1122.33210104703</v>
       </c>
       <c r="AO233" t="n">
         <v>116.087991879472</v>
@@ -38087,10 +38087,10 @@
         <v>0.063</v>
       </c>
       <c r="AY233" t="n">
-        <v>927.243777198955</v>
+        <v>948.728270004151</v>
       </c>
       <c r="AZ233" t="n">
-        <v>151.952036886893</v>
+        <v>152.402604539632</v>
       </c>
     </row>
     <row r="234">
@@ -38122,10 +38122,10 @@
         <v>0.00534192357811758</v>
       </c>
       <c r="J234" t="n">
-        <v>33652.6737904331</v>
+        <v>33677.9706297307</v>
       </c>
       <c r="K234" t="n">
-        <v>22754.8668586682</v>
+        <v>22758.1741078955</v>
       </c>
       <c r="L234" t="n">
         <v>0</v>
@@ -38200,19 +38200,19 @@
         <v>0</v>
       </c>
       <c r="AJ234" t="n">
-        <v>-1542.44282445016</v>
+        <v>-1542.47464713278</v>
       </c>
       <c r="AK234" t="n">
-        <v>-821.188375480322</v>
+        <v>-822.724476688402</v>
       </c>
       <c r="AL234" t="n">
-        <v>-95.6589350064249</v>
+        <v>-96.244777032745</v>
       </c>
       <c r="AM234" t="n">
-        <v>-46.0174202375407</v>
+        <v>-42.4528363916554</v>
       </c>
       <c r="AN234" t="n">
-        <v>567.330478260866</v>
+        <v>563.124225654086</v>
       </c>
       <c r="AO234" t="n">
         <v>58.4651721782414</v>
@@ -38245,10 +38245,10 @@
         <v>0.0441</v>
       </c>
       <c r="AY234" t="n">
-        <v>467.120831992014</v>
+        <v>477.943114719583</v>
       </c>
       <c r="AZ234" t="n">
-        <v>76.4986135209138</v>
+        <v>76.725929678556</v>
       </c>
     </row>
     <row r="235">
@@ -38280,10 +38280,10 @@
         <v>0.00532158987529296</v>
       </c>
       <c r="J235" t="n">
-        <v>33958.7491808582</v>
+        <v>33984.2760981584</v>
       </c>
       <c r="K235" t="n">
-        <v>22959.0539986048</v>
+        <v>22962.3909249014</v>
       </c>
       <c r="L235" t="n">
         <v>0</v>
@@ -38358,16 +38358,16 @@
         <v>0</v>
       </c>
       <c r="AJ235" t="n">
-        <v>-1241.32162748735</v>
+        <v>-1241.3472238903</v>
       </c>
       <c r="AK235" t="n">
-        <v>-659.931118423792</v>
+        <v>-661.16529577887</v>
       </c>
       <c r="AL235" t="n">
-        <v>-95.6589350064249</v>
+        <v>-96.244777032745</v>
       </c>
       <c r="AM235" t="n">
-        <v>-46.0174202375407</v>
+        <v>-42.4528363916554</v>
       </c>
       <c r="AN235" t="n">
         <v>0</v>
@@ -38438,10 +38438,10 @@
         <v>0.00528941636235492</v>
       </c>
       <c r="J236" t="n">
-        <v>34273.6353774192</v>
+        <v>34299.3989958374</v>
       </c>
       <c r="K236" t="n">
-        <v>23174.2404457858</v>
+        <v>23177.6086478185</v>
       </c>
       <c r="L236" t="n">
         <v>0</v>
@@ -38516,16 +38516,16 @@
         <v>0</v>
       </c>
       <c r="AJ236" t="n">
-        <v>-937.731765406951</v>
+        <v>-937.751064500935</v>
       </c>
       <c r="AK236" t="n">
-        <v>-497.267187373284</v>
+        <v>-498.19699197322</v>
       </c>
       <c r="AL236" t="n">
-        <v>-90.9858681442722</v>
+        <v>-91.4968815124153</v>
       </c>
       <c r="AM236" t="n">
-        <v>-40.2693535553485</v>
+        <v>-37.1500242572986</v>
       </c>
       <c r="AN236" t="n">
         <v>0</v>
@@ -38596,10 +38596,10 @@
         <v>0.00524963654830413</v>
       </c>
       <c r="J237" t="n">
-        <v>34595.8305381611</v>
+        <v>34621.8363518728</v>
       </c>
       <c r="K237" t="n">
-        <v>23393.3266473535</v>
+        <v>23396.7266919224</v>
       </c>
       <c r="L237" t="n">
         <v>0</v>
@@ -38674,16 +38674,16 @@
         <v>0</v>
       </c>
       <c r="AJ237" t="n">
-        <v>-631.649632898147</v>
+        <v>-631.662562843596</v>
       </c>
       <c r="AK237" t="n">
-        <v>-333.080062103702</v>
+        <v>-333.702749427502</v>
       </c>
       <c r="AL237" t="n">
-        <v>-77.8416755758108</v>
+        <v>-78.2783226426651</v>
       </c>
       <c r="AM237" t="n">
-        <v>-34.5241687043937</v>
+        <v>-31.8498707228675</v>
       </c>
       <c r="AN237" t="n">
         <v>0</v>
@@ -38754,10 +38754,10 @@
         <v>0.00521033508596069</v>
       </c>
       <c r="J238" t="n">
-        <v>34923.532452738</v>
+        <v>34949.7846011903</v>
       </c>
       <c r="K238" t="n">
-        <v>23622.3122254411</v>
+        <v>23625.7455513463</v>
       </c>
       <c r="L238" t="n">
         <v>0</v>
@@ -38832,16 +38832,16 @@
         <v>0</v>
       </c>
       <c r="AJ238" t="n">
-        <v>-316.797766369311</v>
+        <v>-316.804254507101</v>
       </c>
       <c r="AK238" t="n">
-        <v>-167.283351666757</v>
+        <v>-167.596006465574</v>
       </c>
       <c r="AL238" t="n">
-        <v>-64.7786993236899</v>
+        <v>-65.1414395892984</v>
       </c>
       <c r="AM238" t="n">
-        <v>-28.7720335545722</v>
+        <v>-26.5433052709683</v>
       </c>
       <c r="AN238" t="n">
         <v>0</v>
@@ -38912,10 +38912,10 @@
         <v>0.00516756143130825</v>
       </c>
       <c r="J239" t="n">
-        <v>35254.3381740218</v>
+        <v>35280.8389903578</v>
       </c>
       <c r="K239" t="n">
-        <v>23856.7974571509</v>
+        <v>23860.2648637258</v>
       </c>
       <c r="L239" t="n">
         <v>0</v>
@@ -38996,10 +38996,10 @@
         <v>0</v>
       </c>
       <c r="AL239" t="n">
-        <v>-51.7964375624831</v>
+        <v>-52.0857276876957</v>
       </c>
       <c r="AM239" t="n">
-        <v>-23.0085405992858</v>
+        <v>-21.2262618075968</v>
       </c>
       <c r="AN239" t="n">
         <v>0</v>
@@ -39070,10 +39070,10 @@
         <v>0.00510570215168871</v>
       </c>
       <c r="J240" t="n">
-        <v>35587.0462284486</v>
+        <v>35613.7971426591</v>
       </c>
       <c r="K240" t="n">
-        <v>24088.3828714962</v>
+        <v>24091.8839372741</v>
       </c>
       <c r="L240" t="n">
         <v>0</v>
@@ -39154,10 +39154,10 @@
         <v>0</v>
       </c>
       <c r="AL240" t="n">
-        <v>-38.8943915674805</v>
+        <v>-39.1106853914969</v>
       </c>
       <c r="AM240" t="n">
-        <v>-17.2508113064741</v>
+        <v>-15.9145355440769</v>
       </c>
       <c r="AN240" t="n">
         <v>0</v>
@@ -39228,10 +39228,10 @@
         <v>0.00504465278509314</v>
       </c>
       <c r="J241" t="n">
-        <v>35922.2573528004</v>
+        <v>35949.2602464523</v>
       </c>
       <c r="K241" t="n">
-        <v>24322.7681095038</v>
+        <v>24326.3032414181</v>
       </c>
       <c r="L241" t="n">
         <v>0</v>
@@ -39312,10 +39312,10 @@
         <v>0</v>
       </c>
       <c r="AL241" t="n">
-        <v>-26.0720656955292</v>
+        <v>-26.215814253334</v>
       </c>
       <c r="AM241" t="n">
-        <v>-11.4861317147958</v>
+        <v>-10.5963973630889</v>
       </c>
       <c r="AN241" t="n">
         <v>0</v>
@@ -39386,10 +39386,10 @@
         <v>0.00499215850685553</v>
       </c>
       <c r="J242" t="n">
-        <v>36264.1767045511</v>
+        <v>36291.4366202437</v>
       </c>
       <c r="K242" t="n">
-        <v>24565.8527996047</v>
+        <v>24569.4232620554</v>
       </c>
       <c r="L242" t="n">
         <v>0</v>
@@ -39470,10 +39470,10 @@
         <v>0</v>
       </c>
       <c r="AL242" t="n">
-        <v>-12.9956340326603</v>
+        <v>-13.0672855723492</v>
       </c>
       <c r="AM242" t="n">
-        <v>-5.73247088961341</v>
+        <v>-5.28842441711138</v>
       </c>
       <c r="AN242" t="n">
         <v>0</v>
@@ -39544,10 +39544,10 @@
         <v>0.00493645950017374</v>
       </c>
       <c r="J243" t="n">
-        <v>36612.7041609037</v>
+        <v>36640.2260659737</v>
       </c>
       <c r="K243" t="n">
-        <v>24822.9366080166</v>
+        <v>24826.5444356706</v>
       </c>
       <c r="L243" t="n">
         <v>0</v>
@@ -39702,10 +39702,10 @@
         <v>0.00488530487992378</v>
       </c>
       <c r="J244" t="n">
-        <v>36954.6235126544</v>
+        <v>36982.4024397651</v>
       </c>
       <c r="K244" t="n">
-        <v>25077.6205675751</v>
+        <v>25081.2654116325</v>
       </c>
       <c r="L244" t="n">
         <v>0</v>
@@ -39860,10 +39860,10 @@
         <v>0.00484625476688616</v>
       </c>
       <c r="J245" t="n">
-        <v>37304.252319774</v>
+        <v>37332.2940641515</v>
       </c>
       <c r="K245" t="n">
-        <v>25339.1040988848</v>
+        <v>25342.7869476122</v>
       </c>
       <c r="L245" t="n">
         <v>0</v>
@@ -40018,10 +40018,10 @@
         <v>0.0048076557063792</v>
       </c>
       <c r="J246" t="n">
-        <v>37657.6857931795</v>
+        <v>37685.9932148056</v>
       </c>
       <c r="K246" t="n">
-        <v>25601.3875798122</v>
+        <v>25605.1085494763</v>
       </c>
       <c r="L246" t="n">
         <v>0</v>
@@ -40176,10 +40176,10 @@
         <v>0.00478086441968562</v>
       </c>
       <c r="J247" t="n">
-        <v>38015.224301262</v>
+        <v>38043.8004859064</v>
       </c>
       <c r="K247" t="n">
-        <v>25870.2706450863</v>
+        <v>25874.0306948872</v>
       </c>
       <c r="L247" t="n">
         <v>0</v>
@@ -40334,10 +40334,10 @@
         <v>0.00473926501804089</v>
       </c>
       <c r="J248" t="n">
-        <v>38376.9679668184</v>
+        <v>38405.8160755136</v>
       </c>
       <c r="K248" t="n">
-        <v>26139.0537166581</v>
+        <v>26142.8528320625</v>
       </c>
       <c r="L248" t="n">
         <v>0</v>
@@ -40492,10 +40492,10 @@
         <v>0.00471315781573667</v>
       </c>
       <c r="J249" t="n">
-        <v>38742.9167898488</v>
+        <v>38772.0399836271</v>
       </c>
       <c r="K249" t="n">
-        <v>26409.8366622744</v>
+        <v>26413.6751339489</v>
       </c>
       <c r="L249" t="n">
         <v>0</v>
@@ -40650,10 +40650,10 @@
         <v>0.00467984343253258</v>
       </c>
       <c r="J250" t="n">
-        <v>39112.4700335711</v>
+        <v>39141.8710218889</v>
       </c>
       <c r="K250" t="n">
-        <v>26683.2194441484</v>
+        <v>26687.0976499598</v>
       </c>
       <c r="L250" t="n">
         <v>0</v>
@@ -40808,10 +40808,10 @@
         <v>0.0046431744591946</v>
       </c>
       <c r="J251" t="n">
-        <v>39485.3273295944</v>
+        <v>39515.00859612</v>
       </c>
       <c r="K251" t="n">
-        <v>26959.9020181957</v>
+        <v>26963.820437744</v>
       </c>
       <c r="L251" t="n">
         <v>0</v>
@@ -40966,10 +40966,10 @@
         <v>0.00460321336856051</v>
       </c>
       <c r="J252" t="n">
-        <v>39861.8891691067</v>
+        <v>39891.8534985591</v>
       </c>
       <c r="K252" t="n">
-        <v>27239.6843970119</v>
+        <v>27243.6434808305</v>
       </c>
       <c r="L252" t="n">
         <v>0</v>
@@ -41124,10 +41124,10 @@
         <v>0.00457107075767049</v>
       </c>
       <c r="J253" t="n">
-        <v>40241.8551837169</v>
+        <v>40272.1051350272</v>
       </c>
       <c r="K253" t="n">
-        <v>27522.6665742992</v>
+        <v>27526.6667874548</v>
       </c>
       <c r="L253" t="n">
         <v>0</v>
@@ -41282,10 +41282,10 @@
         <v>0.00449893851450689</v>
       </c>
       <c r="J254" t="n">
-        <v>40622.822426297</v>
+        <v>40653.358752092</v>
       </c>
       <c r="K254" t="n">
-        <v>27807.9486067377</v>
+        <v>27811.9902834969</v>
       </c>
       <c r="L254" t="n">
         <v>0</v>
@@ -41440,10 +41440,10 @@
         <v>0.00453719183232471</v>
       </c>
       <c r="J255" t="n">
-        <v>41008.9960543212</v>
+        <v>41039.82266826</v>
       </c>
       <c r="K255" t="n">
-        <v>28098.5303053938</v>
+        <v>28102.6142160235</v>
       </c>
       <c r="L255" t="n">
         <v>0</v>
@@ -41598,10 +41598,10 @@
         <v>0.00452033241158278</v>
       </c>
       <c r="J256" t="n">
-        <v>41397.9731206613</v>
+        <v>41429.0921300988</v>
       </c>
       <c r="K256" t="n">
-        <v>28392.5117899255</v>
+        <v>28396.638428559</v>
       </c>
       <c r="L256" t="n">
         <v>0</v>
@@ -41756,10 +41756,10 @@
         <v>0.00449275624446099</v>
       </c>
       <c r="J257" t="n">
-        <v>41789.2530113323</v>
+        <v>41820.6661473102</v>
       </c>
       <c r="K257" t="n">
-        <v>28688.5931422038</v>
+        <v>28692.7628140411</v>
       </c>
       <c r="L257" t="n">
         <v>0</v>
@@ -41914,10 +41914,10 @@
         <v>0.00446545931210318</v>
       </c>
       <c r="J258" t="n">
-        <v>42182.9358491313</v>
+        <v>42214.6449179538</v>
       </c>
       <c r="K258" t="n">
-        <v>28986.5743748244</v>
+        <v>28990.7873559989</v>
       </c>
       <c r="L258" t="n">
         <v>0</v>
@@ -42072,10 +42072,10 @@
         <v>0.00443843729721394</v>
       </c>
       <c r="J259" t="n">
-        <v>42579.2218796523</v>
+        <v>42611.2288381489</v>
       </c>
       <c r="K259" t="n">
-        <v>29287.1554437027</v>
+        <v>29291.4121120811</v>
       </c>
       <c r="L259" t="n">
         <v>0</v>
@@ -42230,10 +42230,10 @@
         <v>0.00440811664554808</v>
       </c>
       <c r="J260" t="n">
-        <v>42978.2112256923</v>
+        <v>43010.5181059553</v>
       </c>
       <c r="K260" t="n">
-        <v>29591.4362795632</v>
+        <v>29595.7371728789</v>
       </c>
       <c r="L260" t="n">
         <v>0</v>
